--- a/sample_docs/netflix_subscription.xlsx
+++ b/sample_docs/netflix_subscription.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46316</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="6">
